--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B3E84D6-01DC-40CB-A5E9-92B9962C6F4E}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBC29A61-819C-4AF8-AC53-CF61678DE8F6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Aug</t>
+  </si>
+  <si>
+    <t>I have to focous more</t>
   </si>
 </sst>
 </file>
@@ -489,6 +492,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1034,26 +1041,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46151</v>
+      </c>
+      <c r="B7" s="14">
+        <v>360</v>
+      </c>
+      <c r="C7" s="14">
+        <v>60</v>
+      </c>
+      <c r="D7" s="14">
+        <v>240</v>
+      </c>
+      <c r="E7" s="14">
+        <v>45</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>120</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>615</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53634AA-D7A3-4F7C-8800-36969B18786F}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7511DFE9-F7BE-4FA6-8599-34C6969B191C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t>I have to prepare for my CA</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>I gave Ca very well</t>
   </si>
 </sst>
 </file>
@@ -517,10 +523,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1174,21 +1176,21 @@
         <v>80</v>
       </c>
       <c r="F9" s="13">
+        <v>250</v>
+      </c>
+      <c r="G9" s="13">
         <v>5</v>
-      </c>
-      <c r="G9" s="13">
-        <v>250</v>
       </c>
       <c r="H9" s="13">
         <v>180</v>
       </c>
       <c r="I9" s="14">
         <f t="shared" si="0"/>
-        <v>985</v>
+        <v>1230</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" si="1"/>
-        <v>455</v>
+        <v>210</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>60</v>
@@ -1204,26 +1206,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14" t="str">
+      <c r="A10" s="17">
+        <v>46273</v>
+      </c>
+      <c r="B10" s="13">
+        <v>390</v>
+      </c>
+      <c r="C10" s="13">
+        <v>60</v>
+      </c>
+      <c r="D10" s="13">
+        <v>270</v>
+      </c>
+      <c r="E10" s="13">
+        <v>90</v>
+      </c>
+      <c r="F10" s="13">
+        <v>350</v>
+      </c>
+      <c r="G10" s="13">
+        <v>7</v>
+      </c>
+      <c r="H10" s="13">
+        <v>180</v>
+      </c>
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="14" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="17"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7511DFE9-F7BE-4FA6-8599-34C6969B191C}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53FEA915-4809-4A3B-A27A-49D90D30E963}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -523,6 +523,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1252,25 +1256,47 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14" t="str">
+      <c r="A11" s="17">
+        <v>46274</v>
+      </c>
+      <c r="B11" s="13">
+        <v>330</v>
+      </c>
+      <c r="C11" s="13">
+        <v>60</v>
+      </c>
+      <c r="D11" s="13">
+        <v>300</v>
+      </c>
+      <c r="E11" s="13">
+        <v>90</v>
+      </c>
+      <c r="F11" s="13">
+        <v>300</v>
+      </c>
+      <c r="G11" s="13">
+        <v>6</v>
+      </c>
+      <c r="H11" s="13">
+        <v>200</v>
+      </c>
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="14" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J11" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
+        <v>160</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>61</v>
+      </c>
       <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53FEA915-4809-4A3B-A27A-49D90D30E963}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B9208CB-0313-4BD6-A1A6-EC4703C8D60E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>I gave Ca very well</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -1300,25 +1303,47 @@
       <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14" t="str">
+      <c r="A12" s="12">
+        <v>46275</v>
+      </c>
+      <c r="B12" s="13">
+        <v>360</v>
+      </c>
+      <c r="C12" s="13">
+        <v>60</v>
+      </c>
+      <c r="D12" s="13">
+        <v>180</v>
+      </c>
+      <c r="E12" s="13">
+        <v>60</v>
+      </c>
+      <c r="F12" s="13">
+        <v>100</v>
+      </c>
+      <c r="G12" s="13">
+        <v>2</v>
+      </c>
+      <c r="H12" s="13">
+        <v>200</v>
+      </c>
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
+        <v>480</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B9208CB-0313-4BD6-A1A6-EC4703C8D60E}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{834FDDCF-9D33-4463-AA26-2D9CC904A816}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1347,25 +1347,47 @@
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14" t="str">
+      <c r="A13" s="12">
+        <v>46276</v>
+      </c>
+      <c r="B13" s="13">
+        <v>320</v>
+      </c>
+      <c r="C13" s="13">
+        <v>60</v>
+      </c>
+      <c r="D13" s="13">
+        <v>180</v>
+      </c>
+      <c r="E13" s="13">
+        <v>45</v>
+      </c>
+      <c r="F13" s="13">
+        <v>250</v>
+      </c>
+      <c r="G13" s="13">
+        <v>5</v>
+      </c>
+      <c r="H13" s="13">
+        <v>180</v>
+      </c>
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="14" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
+        <v>405</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="N13" s="16"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5731650e8b717ef2/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{834FDDCF-9D33-4463-AA26-2D9CC904A816}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{497D8C1F-8550-4D6A-82FB-21A58DF8F71D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Done good questions on recursion</t>
   </si>
 </sst>
 </file>
@@ -1390,27 +1393,51 @@
       </c>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14" t="str">
+    <row r="14" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="12">
+        <v>46277</v>
+      </c>
+      <c r="B14" s="13">
+        <v>420</v>
+      </c>
+      <c r="C14" s="13">
+        <v>60</v>
+      </c>
+      <c r="D14" s="13">
+        <v>330</v>
+      </c>
+      <c r="E14" s="13">
+        <v>90</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>240</v>
+      </c>
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="14" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J14" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
